--- a/astro-site/public/dl/plan-negocio-cafeteria/plan-financiero-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria/plan-financiero-cafeteria-brunch.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>0.024966271527407685</v>
       </c>
       <c r="D32" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación, Decoración + iluminación y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación, Decoración + iluminación y Rotulación + imagen "&amp;"exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación, Decoración + iluminación y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E32" s="37" t="inlineStr">
@@ -2432,7 +2432,7 @@
         <v>17692.5</v>
       </c>
       <c r="D37" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
         <v>8887.5</v>
       </c>
       <c r="D42" s="41" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (inocua), Marketing lanzamiento (web + RRSS + Google), Stock inicial (café, leche, bollería, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B35-B40-B41,"0")&amp;" € de los "&amp;TEXT(B35,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (inocua), Marketing lanzamiento (web + RRSS + Google), Stock inicial (café, leche, bollería, etc.), Fianza del alquiler, Alquiler de los "&amp;"meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B35-B40-B41,"0")&amp;" € de los "&amp;TEXT(B35,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (inocua), Marketing lanzamiento (web + RRSS + Google), Stock inicial (café, leche, bollería, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 51926 € de los 130176 € de inversión.</v>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="32" t="n"/>

--- a/astro-site/public/dl/plan-negocio-cafeteria/plan-financiero-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria/plan-financiero-cafeteria-brunch.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-cafeteria/plan-financiero-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria/plan-financiero-cafeteria-brunch.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>0.024966271527407685</v>
       </c>
       <c r="D32" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación, Decoración + iluminación y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación, Decoración + iluminación y Rotulación + imagen "&amp;"exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica + climatización, Fontanería + evacuación, Decoración + iluminación y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E32" s="37" t="inlineStr">
@@ -2432,7 +2432,7 @@
         <v>17692.5</v>
       </c>
       <c r="D37" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
         <v>8887.5</v>
       </c>
       <c r="D42" s="41" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (inocua), Marketing lanzamiento (web + RRSS + Google), Stock inicial (café, leche, bollería, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B35-B40-B41,"0")&amp;" € de los "&amp;TEXT(B35,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (inocua), Marketing lanzamiento (web + RRSS + Google), Stock inicial (café, leche, bollería, etc.), Fianza del alquiler, Alquiler de los "&amp;"meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B35-B40-B41,"0")&amp;" € de los "&amp;TEXT(B35,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencia de actividad (inocua), Marketing lanzamiento (web + RRSS + Google), Stock inicial (café, leche, bollería, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 51926 € de los 130176 € de inversión.</v>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="32" t="n"/>
